--- a/data/trans_camb/P16A08-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A08-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 4,45</t>
+          <t>-1,3; 4,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 4,37</t>
+          <t>-1,32; 4,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 9,57</t>
+          <t>0,39; 9,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,26</t>
+          <t>2,33; 9,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 6,04</t>
+          <t>0,08; 6,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,07</t>
+          <t>-1,88; 2,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,93</t>
+          <t>1,04; 5,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 4,51</t>
+          <t>0,14; 4,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 5,2</t>
+          <t>0,12; 5,56</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-49,51; 422,9</t>
+          <t>-41,83; 490,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-44,84; 353,07</t>
+          <t>-42,98; 486,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 850,89</t>
+          <t>-15,6; 681,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38,73; 1452,98</t>
+          <t>52,72; 1816,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 1036,02</t>
+          <t>-14,79; 1177,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,88; 453,81</t>
+          <t>-65,99; 445,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,15; 512,37</t>
+          <t>33,08; 544,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 417,08</t>
+          <t>-1,14; 379,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 415,81</t>
+          <t>-6,31; 435,48</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,45</t>
+          <t>1,47; 7,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,65</t>
+          <t>-1,57; 2,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 5,61</t>
+          <t>0,01; 5,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 4,12</t>
+          <t>-2,1; 4,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 3,74</t>
+          <t>-2,29; 3,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,81</t>
+          <t>-3,65; 1,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,84</t>
+          <t>0,43; 4,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,46</t>
+          <t>-1,44; 2,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,74</t>
+          <t>-1,17; 2,76</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,01; 557,86</t>
+          <t>29,82; 581,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,0; 216,44</t>
+          <t>-48,1; 204,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 420,05</t>
+          <t>-11,17; 422,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 89,2</t>
+          <t>-30,3; 84,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 81,32</t>
+          <t>-30,21; 79,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,3; 42,72</t>
+          <t>-45,87; 38,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 139,8</t>
+          <t>6,3; 136,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,46; 77,06</t>
+          <t>-28,16; 70,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,52; 81,5</t>
+          <t>-23,24; 83,64</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,31</t>
+          <t>-0,6; 3,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,46</t>
+          <t>0,02; 4,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 5,49</t>
+          <t>-0,04; 5,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 7,85</t>
+          <t>1,33; 8,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,83</t>
+          <t>-2,09; 2,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,62</t>
+          <t>-2,48; 1,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,03</t>
+          <t>1,3; 5,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,84</t>
+          <t>-0,49; 2,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,83</t>
+          <t>-0,71; 2,77</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-93,82; —</t>
+          <t>-84,99; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,5; —</t>
+          <t>-53,71; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,18; —</t>
+          <t>-62,42; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,71; 578,06</t>
+          <t>26,65; 583,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,23; 215,48</t>
+          <t>-52,9; 215,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,03; 113,06</t>
+          <t>-65,53; 140,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,88; 459,52</t>
+          <t>32,54; 485,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 327,04</t>
+          <t>-23,82; 294,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 274,33</t>
+          <t>-33,76; 258,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 1,55</t>
+          <t>-2,99; 1,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 5,14</t>
+          <t>-1,07; 4,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 2,01</t>
+          <t>-3,33; 2,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 3,14</t>
+          <t>-2,07; 3,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 6,28</t>
+          <t>-0,32; 6,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 45,62</t>
+          <t>-1,78; 44,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,75</t>
+          <t>-1,92; 1,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,77</t>
+          <t>0,24; 4,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 32,69</t>
+          <t>-1,39; 32,44</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-75,21; 144,59</t>
+          <t>-78,67; 147,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 449,04</t>
+          <t>-35,65; 343,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-88,69; 172,4</t>
+          <t>-85,35; 196,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,43; 134,43</t>
+          <t>-43,81; 193,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 263,8</t>
+          <t>-10,5; 285,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,21; 2497,07</t>
+          <t>-44,22; 2113,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-48,03; 80,93</t>
+          <t>-45,82; 79,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 217,79</t>
+          <t>3,16; 210,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,45; 1465,21</t>
+          <t>-41,48; 1390,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 4,35</t>
+          <t>-2,72; 4,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 1,5</t>
+          <t>-4,81; 1,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 4,03</t>
+          <t>-3,3; 4,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 7,3</t>
+          <t>-4,98; 6,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 0,67</t>
+          <t>-9,31; 0,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,76; -0,73</t>
+          <t>-9,95; -0,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 4,33</t>
+          <t>-2,59; 4,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 0,25</t>
+          <t>-5,58; 0,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 0,74</t>
+          <t>-4,97; 0,75</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-58,37; 258,85</t>
+          <t>-59,93; 312,06</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-84,05; 136,16</t>
+          <t>-85,31; 153,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-69,6; 275,43</t>
+          <t>-68,55; 248,26</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-38,56; 141,97</t>
+          <t>-44,12; 120,55</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-77,69; 18,32</t>
+          <t>-76,7; 26,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-76,87; -7,7</t>
+          <t>-77,98; -8,24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-33,48; 108,54</t>
+          <t>-34,58; 106,53</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-71,64; 10,45</t>
+          <t>-69,86; 12,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-66,17; 23,39</t>
+          <t>-64,33; 24,51</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 5,25</t>
+          <t>-0,91; 4,98</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 5,03</t>
+          <t>-0,76; 4,73</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 3,46</t>
+          <t>-1,91; 3,07</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 5,13</t>
+          <t>-1,85; 5,56</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 5,58</t>
+          <t>-2,26; 5,14</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,39</t>
+          <t>-3,04; 3,38</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,39</t>
+          <t>-0,6; 4,05</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,14</t>
+          <t>-0,53; 4,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,45</t>
+          <t>-1,75; 2,48</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-46,89; 825,11</t>
+          <t>-45,23; 657,52</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-46,81; 805,0</t>
+          <t>-39,84; 658,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-74,53; 546,38</t>
+          <t>-72,22; 437,71</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-38,38; 262,84</t>
+          <t>-45,28; 288,3</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 301,52</t>
+          <t>-51,17; 270,9</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 193,06</t>
+          <t>-58,93; 212,16</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 254,66</t>
+          <t>-20,28; 240,02</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 239,55</t>
+          <t>-16,37; 246,1</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-42,57; 149,87</t>
+          <t>-46,54; 168,14</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,37</t>
+          <t>-1,41; 1,44</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,35</t>
+          <t>-0,98; 2,48</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 2,87</t>
+          <t>-0,41; 3,13</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,37</t>
+          <t>-0,84; 3,26</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,35</t>
+          <t>0,78; 5,2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 5,3</t>
+          <t>-0,91; 5,43</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,88</t>
+          <t>-0,62; 1,98</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,36</t>
+          <t>0,36; 3,24</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,1; 3,61</t>
+          <t>0,28; 3,77</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-61,76; 169,71</t>
+          <t>-62,57; 180,34</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-47,57; 262,03</t>
+          <t>-52,63; 258,7</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,4; 341,52</t>
+          <t>-32,46; 347,04</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-22,87; 170,73</t>
+          <t>-24,75; 162,14</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>15,85; 279,21</t>
+          <t>21,27; 268,75</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 246,34</t>
+          <t>-12,13; 245,43</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-28,48; 108,86</t>
+          <t>-22,98; 119,04</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>17,38; 196,22</t>
+          <t>10,66; 195,56</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6,71; 196,44</t>
+          <t>15,03; 221,86</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,88</t>
+          <t>-2,12; 1,85</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,26</t>
+          <t>-2,52; 1,21</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,65</t>
+          <t>-3,7; 0,83</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,36</t>
+          <t>-1,51; 2,42</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,43</t>
+          <t>-0,64; 3,41</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,17</t>
+          <t>0,32; 4,38</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,68</t>
+          <t>-1,02; 1,82</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,87</t>
+          <t>-0,94; 1,93</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,9</t>
+          <t>-1,77; 1,7</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-42,21; 68,44</t>
+          <t>-44,16; 65,23</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-52,61; 46,19</t>
+          <t>-51,2; 42,57</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-74,51; 20,63</t>
+          <t>-74,07; 26,58</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-34,88; 83,15</t>
+          <t>-30,17; 89,23</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 125,49</t>
+          <t>-13,45; 128,66</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,9; 147,69</t>
+          <t>4,8; 163,77</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 58,75</t>
+          <t>-23,78; 61,95</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 57,84</t>
+          <t>-21,5; 63,59</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-32,93; 59,43</t>
+          <t>-38,78; 52,32</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,88</t>
+          <t>0,18; 1,85</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,4</t>
+          <t>-0,06; 1,57</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,86</t>
+          <t>-0,12; 1,88</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,67</t>
+          <t>0,65; 2,6</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,56</t>
+          <t>0,4; 2,44</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,25; 8,91</t>
+          <t>0,23; 9,71</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,98</t>
+          <t>0,63; 2,02</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,74</t>
+          <t>0,46; 1,82</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,37</t>
+          <t>0,47; 4,89</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>7,65; 96,05</t>
+          <t>5,3; 91,58</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 68,55</t>
+          <t>-2,85; 80,58</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 91,51</t>
+          <t>-4,78; 91,82</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>14,64; 80,68</t>
+          <t>14,54; 73,49</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>11,81; 75,47</t>
+          <t>9,13; 71,14</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,96; 253,6</t>
+          <t>4,68; 235,28</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>19,21; 69,95</t>
+          <t>18,32; 72,09</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>11,56; 59,29</t>
+          <t>12,58; 62,45</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>12,63; 164,9</t>
+          <t>14,3; 158,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A08-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A08-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,05</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>1,34</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>2,11</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 4,64</t>
+          <t>-1,54; 4,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,55</t>
+          <t>-1,4; 4,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 9,47</t>
+          <t>-0,31; 6,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 9,04</t>
+          <t>2,28; 9,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 6,14</t>
+          <t>0,31; 6,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,1</t>
+          <t>-0,9; 4,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,97</t>
+          <t>0,96; 5,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 4,52</t>
+          <t>0,31; 4,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,56</t>
+          <t>0,03; 4,38</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>175,55%</t>
+          <t>124,81%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>115,46%</t>
+          <t>107,99%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,83; 490,63</t>
+          <t>-53,18; 415,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,98; 486,94</t>
+          <t>-52,09; 383,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 681,71</t>
+          <t>-24,79; 604,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52,72; 1816,64</t>
+          <t>49,54; 1680,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 1177,74</t>
+          <t>-5,75; 1388,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,99; 445,56</t>
+          <t>-52,61; 673,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,08; 544,87</t>
+          <t>18,85; 506,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 379,4</t>
+          <t>-0,9; 379,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 435,48</t>
+          <t>-9,58; 345,5</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>2,39</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-0,97</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 7,27</t>
+          <t>1,54; 7,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,7</t>
+          <t>-1,36; 2,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 5,52</t>
+          <t>-0,15; 5,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 4,13</t>
+          <t>-2,16; 3,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,71</t>
+          <t>-2,55; 3,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 1,82</t>
+          <t>-3,77; 1,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,64</t>
+          <t>0,47; 4,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 2,4</t>
+          <t>-1,2; 2,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,76</t>
+          <t>-1,56; 2,51</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114,18%</t>
+          <t>108,16%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-15,12%</t>
+          <t>-15,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,82; 581,33</t>
+          <t>40,73; 566,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 204,25</t>
+          <t>-46,07; 218,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 422,39</t>
+          <t>-11,75; 391,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,3; 84,27</t>
+          <t>-27,95; 84,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 79,15</t>
+          <t>-32,97; 78,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,87; 38,91</t>
+          <t>-46,28; 29,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 136,88</t>
+          <t>8,99; 138,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 70,66</t>
+          <t>-23,01; 74,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 83,64</t>
+          <t>-30,07; 68,54</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>2,24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,9</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,32</t>
+          <t>-0,56; 3,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 4,49</t>
+          <t>0,33; 4,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 5,35</t>
+          <t>0,09; 4,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 8,18</t>
+          <t>1,39; 8,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 2,83</t>
+          <t>-2,1; 2,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 1,78</t>
+          <t>-2,69; 1,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,37</t>
+          <t>1,24; 5,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,99</t>
+          <t>-0,35; 2,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,77</t>
+          <t>-0,59; 2,54</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>274,66%</t>
+          <t>280,86%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-11,48%</t>
+          <t>-13,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,02%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-84,99; —</t>
+          <t>-71,1; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-53,71; —</t>
+          <t>-48,38; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,42; —</t>
+          <t>-64,39; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,65; 583,77</t>
+          <t>30,23; 580,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,9; 215,24</t>
+          <t>-59,18; 161,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,53; 140,58</t>
+          <t>-66,17; 129,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,54; 485,07</t>
+          <t>43,06; 479,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,82; 294,76</t>
+          <t>-21,29; 263,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-33,76; 258,54</t>
+          <t>-27,71; 257,28</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,35</t>
+          <t>-0,57</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7,84</t>
+          <t>-0,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,7</t>
+          <t>-2,96; 1,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,54</t>
+          <t>-1,01; 4,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 2,07</t>
+          <t>-3,07; 2,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 3,58</t>
+          <t>-1,86; 3,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 6,38</t>
+          <t>-0,21; 6,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 44,31</t>
+          <t>-2,97; 2,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,76</t>
+          <t>-1,78; 1,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 4,75</t>
+          <t>0,14; 4,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 32,44</t>
+          <t>-2,29; 1,34</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-29,87%</t>
+          <t>-21,31%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>378,8%</t>
+          <t>-16,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>255,49%</t>
+          <t>-17,69%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-78,67; 147,01</t>
+          <t>-76,67; 147,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,65; 343,16</t>
+          <t>-33,08; 333,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-85,35; 196,93</t>
+          <t>-81,36; 199,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,81; 193,37</t>
+          <t>-43,0; 155,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 285,05</t>
+          <t>-9,43; 280,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,22; 2113,21</t>
+          <t>-63,06; 108,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-45,82; 79,95</t>
+          <t>-44,61; 80,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,16; 210,01</t>
+          <t>2,26; 210,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,48; 1390,92</t>
+          <t>-57,79; 62,54</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,55</t>
+          <t>-4,63</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,18</t>
+          <t>-2,36</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 4,92</t>
+          <t>-3,0; 4,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 1,8</t>
+          <t>-4,42; 1,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 4,31</t>
+          <t>-3,67; 3,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 6,65</t>
+          <t>-4,73; 6,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 0,97</t>
+          <t>-8,9; 1,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,95; -0,74</t>
+          <t>-10,09; -0,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 4,34</t>
+          <t>-2,36; 4,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 0,37</t>
+          <t>-5,69; 0,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 0,75</t>
+          <t>-5,48; 0,51</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>-2,25%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-53,61%</t>
+          <t>-54,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-36,74%</t>
+          <t>-39,86%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-59,93; 312,06</t>
+          <t>-61,74; 259,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-85,31; 153,0</t>
+          <t>-86,3; 145,92</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-68,55; 248,26</t>
+          <t>-72,36; 233,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-44,12; 120,55</t>
+          <t>-42,0; 125,92</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-76,7; 26,3</t>
+          <t>-74,92; 27,92</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-77,98; -8,24</t>
+          <t>-78,96; -3,14</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-34,58; 106,53</t>
+          <t>-30,32; 110,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-69,86; 12,52</t>
+          <t>-70,3; 16,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-64,33; 24,51</t>
+          <t>-66,77; 16,58</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,49</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,98</t>
+          <t>-0,65; 5,06</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 4,73</t>
+          <t>-1,1; 4,9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 3,07</t>
+          <t>-1,97; 3,48</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 5,56</t>
+          <t>-1,67; 5,13</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 5,14</t>
+          <t>-2,03; 5,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 3,38</t>
+          <t>-2,91; 3,18</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,05</t>
+          <t>-0,31; 4,15</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 4,0</t>
+          <t>-0,44; 4,09</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,48</t>
+          <t>-1,39; 2,53</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-45,23; 657,52</t>
+          <t>-43,98; 908,65</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-39,84; 658,87</t>
+          <t>-43,95; 789,83</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-72,22; 437,71</t>
+          <t>-68,83; 581,7</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-45,28; 288,3</t>
+          <t>-37,95; 267,47</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-51,17; 270,9</t>
+          <t>-46,32; 261,47</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-58,93; 212,16</t>
+          <t>-56,91; 173,87</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 240,02</t>
+          <t>-10,68; 252,37</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 246,1</t>
+          <t>-16,6; 236,99</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-46,54; 168,14</t>
+          <t>-42,94; 164,03</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>4,46</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>3,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,44</t>
+          <t>-1,56; 1,39</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,48</t>
+          <t>-0,99; 2,55</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 3,13</t>
+          <t>-0,08; 3,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,26</t>
+          <t>-0,8; 3,27</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,2</t>
+          <t>0,62; 5,15</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 5,43</t>
+          <t>2,4; 6,84</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,98</t>
+          <t>-0,63; 1,88</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,24</t>
+          <t>0,53; 3,31</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,77</t>
+          <t>1,55; 4,42</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>154,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>137,45%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-62,57; 180,34</t>
+          <t>-67,85; 167,96</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-52,63; 258,7</t>
+          <t>-49,81; 288,09</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-32,46; 347,04</t>
+          <t>-12,62; 417,24</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 162,14</t>
+          <t>-20,17; 183,71</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>21,27; 268,75</t>
+          <t>11,7; 245,24</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 245,43</t>
+          <t>53,22; 352,56</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-22,98; 119,04</t>
+          <t>-23,03; 115,37</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>10,66; 195,56</t>
+          <t>15,55; 199,37</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>15,03; 221,86</t>
+          <t>48,42; 261,04</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-1,3</t>
+          <t>-0,53</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>2,42</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,97</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,85</t>
+          <t>-1,91; 2,11</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,21</t>
+          <t>-2,51; 1,25</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,83</t>
+          <t>-2,4; 1,48</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,42</t>
+          <t>-1,54; 2,39</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,41</t>
+          <t>-0,78; 3,56</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,38</t>
+          <t>0,47; 4,45</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,82</t>
+          <t>-1,24; 1,51</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,93</t>
+          <t>-1,04; 1,76</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,7</t>
+          <t>-0,45; 2,38</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-34,17%</t>
+          <t>-14,03%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-44,16; 65,23</t>
+          <t>-40,36; 78,59</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 42,57</t>
+          <t>-50,37; 47,95</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-74,07; 26,58</t>
+          <t>-50,89; 52,03</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-30,17; 89,23</t>
+          <t>-32,86; 89,52</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 128,66</t>
+          <t>-17,38; 129,68</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,8; 163,77</t>
+          <t>7,83; 154,43</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 61,95</t>
+          <t>-27,11; 48,19</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 63,59</t>
+          <t>-23,48; 56,07</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-38,78; 52,32</t>
+          <t>-10,4; 78,26</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>1,03</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,85</t>
+          <t>0,18; 1,87</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,57</t>
+          <t>-0,06; 1,49</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,88</t>
+          <t>0,21; 1,9</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,6</t>
+          <t>0,59; 2,64</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,44</t>
+          <t>0,42; 2,45</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,23; 9,71</t>
+          <t>0,2; 1,99</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,02</t>
+          <t>0,63; 1,99</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,82</t>
+          <t>0,47; 1,74</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,89</t>
+          <t>0,44; 1,67</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>5,3; 91,58</t>
+          <t>6,84; 94,11</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 80,58</t>
+          <t>-3,24; 73,57</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 91,82</t>
+          <t>6,55; 97,89</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>14,54; 73,49</t>
+          <t>12,61; 75,44</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>9,13; 71,14</t>
+          <t>9,21; 70,27</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,68; 235,28</t>
+          <t>4,44; 60,77</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>18,32; 72,09</t>
+          <t>18,32; 69,79</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>12,58; 62,45</t>
+          <t>13,65; 61,64</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>14,3; 158,08</t>
+          <t>12,79; 58,1</t>
         </is>
       </c>
     </row>
